--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/41.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/41.xlsx
@@ -426,13 +426,13 @@
         <v>-11.29867233332798</v>
       </c>
       <c r="E2">
-        <v>-6.845918129329257</v>
+        <v>-6.428673591210526</v>
       </c>
       <c r="F2">
-        <v>-0.1172812325032646</v>
+        <v>-0.756623477657951</v>
       </c>
       <c r="G2">
-        <v>-6.828514459973745</v>
+        <v>-6.684485865742212</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.63572160109843</v>
       </c>
       <c r="E3">
-        <v>-7.828986437758385</v>
+        <v>-8.166235482531619</v>
       </c>
       <c r="F3">
-        <v>-0.3337849936337489</v>
+        <v>-1.085692428420055</v>
       </c>
       <c r="G3">
-        <v>-5.928195047841249</v>
+        <v>-6.040842980906029</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.946300225360256</v>
       </c>
       <c r="E4">
-        <v>-8.656614875874226</v>
+        <v>-8.914570340773153</v>
       </c>
       <c r="F4">
-        <v>-0.3721234937701157</v>
+        <v>-0.991150856738547</v>
       </c>
       <c r="G4">
-        <v>-6.04388537225662</v>
+        <v>-6.451416838686442</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.331601291226443</v>
       </c>
       <c r="E5">
-        <v>-8.565642361534136</v>
+        <v>-8.722753238756253</v>
       </c>
       <c r="F5">
-        <v>-0.3005243856765432</v>
+        <v>-1.094680214740429</v>
       </c>
       <c r="G5">
-        <v>-5.760562263914712</v>
+        <v>-5.576565453387559</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.777723339894223</v>
       </c>
       <c r="E6">
-        <v>-9.21964457772189</v>
+        <v>-8.917608946832299</v>
       </c>
       <c r="F6">
-        <v>-0.2023852143646774</v>
+        <v>-0.8902904985084849</v>
       </c>
       <c r="G6">
-        <v>-5.33163805221012</v>
+        <v>-5.297896972073868</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.308455923249442</v>
       </c>
       <c r="E7">
-        <v>-10.1341608466229</v>
+        <v>-10.89096847973279</v>
       </c>
       <c r="F7">
-        <v>-0.4229189829097814</v>
+        <v>-0.8980539578075217</v>
       </c>
       <c r="G7">
-        <v>-4.785934346607736</v>
+        <v>-4.725857876706582</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.921915821416142</v>
       </c>
       <c r="E8">
-        <v>-11.57286156733378</v>
+        <v>-11.93758486391155</v>
       </c>
       <c r="F8">
-        <v>-0.3363993211569842</v>
+        <v>-0.9655410501135975</v>
       </c>
       <c r="G8">
-        <v>-4.586291897861987</v>
+        <v>-4.472750117501604</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.616696712360452</v>
       </c>
       <c r="E9">
-        <v>-12.32490071731359</v>
+        <v>-12.52452490851972</v>
       </c>
       <c r="F9">
-        <v>-0.2522338795629432</v>
+        <v>-1.079648659849229</v>
       </c>
       <c r="G9">
-        <v>-3.980852708548994</v>
+        <v>-4.477017410701723</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.388950208776887</v>
       </c>
       <c r="E10">
-        <v>-13.02990260777573</v>
+        <v>-12.40309840647804</v>
       </c>
       <c r="F10">
-        <v>-0.693686607495453</v>
+        <v>-0.9498857345680897</v>
       </c>
       <c r="G10">
-        <v>-3.359526211193038</v>
+        <v>-3.876133532050768</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.218581964652426</v>
       </c>
       <c r="E11">
-        <v>-12.66148860488171</v>
+        <v>-13.70209117557829</v>
       </c>
       <c r="F11">
-        <v>-0.3887156928481897</v>
+        <v>-1.115532707371101</v>
       </c>
       <c r="G11">
-        <v>-2.731350195116331</v>
+        <v>-3.683036031836158</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.102006468556765</v>
       </c>
       <c r="E12">
-        <v>-14.05293017084854</v>
+        <v>-13.79526905676011</v>
       </c>
       <c r="F12">
-        <v>-0.3671665432317634</v>
+        <v>-1.114006026247742</v>
       </c>
       <c r="G12">
-        <v>-2.727814532480389</v>
+        <v>-2.96087693844508</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.012969345854684</v>
       </c>
       <c r="E13">
-        <v>-14.16373740134222</v>
+        <v>-15.58862627632971</v>
       </c>
       <c r="F13">
-        <v>-0.3428241387330971</v>
+        <v>-0.8472766927507177</v>
       </c>
       <c r="G13">
-        <v>-2.584894971004513</v>
+        <v>-1.737961416238304</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.947375879107265</v>
       </c>
       <c r="E14">
-        <v>-15.69586054083134</v>
+        <v>-16.24540897555817</v>
       </c>
       <c r="F14">
-        <v>-0.3679104171594774</v>
+        <v>-0.6982948153572266</v>
       </c>
       <c r="G14">
-        <v>-2.553087249463195</v>
+        <v>-2.361221272189194</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.883117566585105</v>
       </c>
       <c r="E15">
-        <v>-16.52177721577229</v>
+        <v>-16.25707885307594</v>
       </c>
       <c r="F15">
-        <v>0.09241749041322189</v>
+        <v>-0.669772468944034</v>
       </c>
       <c r="G15">
-        <v>-1.690024716829657</v>
+        <v>-1.352418593280321</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.809685071670724</v>
       </c>
       <c r="E16">
-        <v>-17.14997165859033</v>
+        <v>-18.03135761165122</v>
       </c>
       <c r="F16">
-        <v>0.2175291327276424</v>
+        <v>-0.5470456963822733</v>
       </c>
       <c r="G16">
-        <v>-1.445600518574187</v>
+        <v>-1.077371848786592</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.713996014351556</v>
       </c>
       <c r="E17">
-        <v>-18.14048024981406</v>
+        <v>-17.99219083995888</v>
       </c>
       <c r="F17">
-        <v>0.4690347300960171</v>
+        <v>-0.361755647356677</v>
       </c>
       <c r="G17">
-        <v>-1.428955095602731</v>
+        <v>-1.102343293789315</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.586250657099986</v>
       </c>
       <c r="E18">
-        <v>-18.70260425686019</v>
+        <v>-18.72596212579175</v>
       </c>
       <c r="F18">
-        <v>0.8214942912109704</v>
+        <v>0.1387679600694654</v>
       </c>
       <c r="G18">
-        <v>-0.823770818296262</v>
+        <v>-0.8875981362934104</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.429734203397927</v>
       </c>
       <c r="E19">
-        <v>-19.43241765641035</v>
+        <v>-19.63498988419547</v>
       </c>
       <c r="F19">
-        <v>1.107923858281372</v>
+        <v>0.1144885114934119</v>
       </c>
       <c r="G19">
-        <v>-0.1331248078935069</v>
+        <v>-0.4712639292746659</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.242863386828347</v>
       </c>
       <c r="E20">
-        <v>-20.34370512334389</v>
+        <v>-20.01764593784361</v>
       </c>
       <c r="F20">
-        <v>1.328201661299011</v>
+        <v>0.4582618120226096</v>
       </c>
       <c r="G20">
-        <v>-0.4450477191491774</v>
+        <v>-1.140358288216766</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.044938488558175</v>
       </c>
       <c r="E21">
-        <v>-21.87564712387271</v>
+        <v>-20.94651294087493</v>
       </c>
       <c r="F21">
-        <v>1.437388768662014</v>
+        <v>0.6118129640099427</v>
       </c>
       <c r="G21">
-        <v>-0.1169991405717169</v>
+        <v>-0.9311516734080622</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.840758203068286</v>
       </c>
       <c r="E22">
-        <v>-21.68858039108985</v>
+        <v>-21.1301063340939</v>
       </c>
       <c r="F22">
-        <v>1.948860908050958</v>
+        <v>1.1682952745974</v>
       </c>
       <c r="G22">
-        <v>-0.7958496772180488</v>
+        <v>-0.1307875627427814</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.655055217621497</v>
       </c>
       <c r="E23">
-        <v>-20.72154288064788</v>
+        <v>-21.65922682257213</v>
       </c>
       <c r="F23">
-        <v>2.175651335589406</v>
+        <v>1.638696958155544</v>
       </c>
       <c r="G23">
-        <v>-0.4828342859344187</v>
+        <v>-0.2401117080861338</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.498097679257831</v>
       </c>
       <c r="E24">
-        <v>-22.34012817436545</v>
+        <v>-22.53978406488962</v>
       </c>
       <c r="F24">
-        <v>2.315380349093627</v>
+        <v>1.675459903491786</v>
       </c>
       <c r="G24">
-        <v>-1.367739798036068</v>
+        <v>-0.6183812624943382</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.389931078678885</v>
       </c>
       <c r="E25">
-        <v>-22.41060481534682</v>
+        <v>-23.58918998905711</v>
       </c>
       <c r="F25">
-        <v>2.65183171014948</v>
+        <v>1.68183170555412</v>
       </c>
       <c r="G25">
-        <v>-0.8091713124680759</v>
+        <v>-0.7633864676599554</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.343073546811672</v>
       </c>
       <c r="E26">
-        <v>-22.74822972346269</v>
+        <v>-22.89727991695115</v>
       </c>
       <c r="F26">
-        <v>2.832276638236102</v>
+        <v>1.875391346361864</v>
       </c>
       <c r="G26">
-        <v>-1.354355262420794</v>
+        <v>-1.348081778623875</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.365697761550162</v>
       </c>
       <c r="E27">
-        <v>-22.02971486656167</v>
+        <v>-23.01045553935085</v>
       </c>
       <c r="F27">
-        <v>2.887982689339563</v>
+        <v>1.873669998898846</v>
       </c>
       <c r="G27">
-        <v>-1.690570956843637</v>
+        <v>-1.754769055941184</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.466338976285833</v>
       </c>
       <c r="E28">
-        <v>-22.36875718704194</v>
+        <v>-22.30165425919628</v>
       </c>
       <c r="F28">
-        <v>3.010534676379333</v>
+        <v>2.199746886602038</v>
       </c>
       <c r="G28">
-        <v>-1.843624098215222</v>
+        <v>-2.317243985245515</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.635754214851627</v>
       </c>
       <c r="E29">
-        <v>-21.5906068559339</v>
+        <v>-22.6902561992165</v>
       </c>
       <c r="F29">
-        <v>3.156123560890957</v>
+        <v>2.082614079111382</v>
       </c>
       <c r="G29">
-        <v>-2.095093137378262</v>
+        <v>-2.097013253791039</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.8732210869228</v>
       </c>
       <c r="E30">
-        <v>-21.42273632446956</v>
+        <v>-22.36037498165374</v>
       </c>
       <c r="F30">
-        <v>3.307481195995677</v>
+        <v>2.236721893993397</v>
       </c>
       <c r="G30">
-        <v>-3.017265460615486</v>
+        <v>-2.463523750443752</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.15322589527496</v>
       </c>
       <c r="E31">
-        <v>-21.93601621086896</v>
+        <v>-21.49640553962634</v>
       </c>
       <c r="F31">
-        <v>3.168860538076402</v>
+        <v>2.354393140295872</v>
       </c>
       <c r="G31">
-        <v>-2.957642535453212</v>
+        <v>-2.77178188778745</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.463376389421173</v>
       </c>
       <c r="E32">
-        <v>-21.70536744423628</v>
+        <v>-21.57092610789657</v>
       </c>
       <c r="F32">
-        <v>3.026802155435509</v>
+        <v>1.837084324186803</v>
       </c>
       <c r="G32">
-        <v>-3.272465484601284</v>
+        <v>-3.033036899564574</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.772768774861519</v>
       </c>
       <c r="E33">
-        <v>-21.43625834785647</v>
+        <v>-21.78425798992391</v>
       </c>
       <c r="F33">
-        <v>2.983866216213606</v>
+        <v>2.011483826967794</v>
       </c>
       <c r="G33">
-        <v>-3.242657332565687</v>
+        <v>-2.804433798441281</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.059411709552376</v>
       </c>
       <c r="E34">
-        <v>-20.82471963243864</v>
+        <v>-21.04120786084933</v>
       </c>
       <c r="F34">
-        <v>2.788386419766173</v>
+        <v>1.800120913939084</v>
       </c>
       <c r="G34">
-        <v>-2.782034647322572</v>
+        <v>-2.525927533859014</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.296626841683007</v>
       </c>
       <c r="E35">
-        <v>-20.23846791587964</v>
+        <v>-20.99532536220361</v>
       </c>
       <c r="F35">
-        <v>3.067569428796884</v>
+        <v>2.114618882085944</v>
       </c>
       <c r="G35">
-        <v>-2.964717171270635</v>
+        <v>-2.960522710072378</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.462119337727168</v>
       </c>
       <c r="E36">
-        <v>-19.64727110570427</v>
+        <v>-20.46163564345164</v>
       </c>
       <c r="F36">
-        <v>2.776991397773263</v>
+        <v>2.00176210712854</v>
       </c>
       <c r="G36">
-        <v>-3.153070659727469</v>
+        <v>-3.045858642438172</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.543230922897844</v>
       </c>
       <c r="E37">
-        <v>-19.19224098046553</v>
+        <v>-19.35309237721799</v>
       </c>
       <c r="F37">
-        <v>2.509326009111075</v>
+        <v>1.817047773447889</v>
       </c>
       <c r="G37">
-        <v>-2.778035508311133</v>
+        <v>-3.199878463107225</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.528424254193712</v>
       </c>
       <c r="E38">
-        <v>-19.50168972330568</v>
+        <v>-19.40563173265498</v>
       </c>
       <c r="F38">
-        <v>2.329275383908186</v>
+        <v>2.046379632178127</v>
       </c>
       <c r="G38">
-        <v>-3.474183645400156</v>
+        <v>-2.563925975558769</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.426377003297047</v>
       </c>
       <c r="E39">
-        <v>-19.07115864244845</v>
+        <v>-18.54508128850337</v>
       </c>
       <c r="F39">
-        <v>2.188636822995691</v>
+        <v>1.909062824550858</v>
       </c>
       <c r="G39">
-        <v>-2.388440577613081</v>
+        <v>-2.471988815387669</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.239862690653234</v>
       </c>
       <c r="E40">
-        <v>-17.83244891933831</v>
+        <v>-18.20734316853731</v>
       </c>
       <c r="F40">
-        <v>2.195898291648632</v>
+        <v>1.629273450581297</v>
       </c>
       <c r="G40">
-        <v>-2.766296313828877</v>
+        <v>-2.755401308459136</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.992072159695445</v>
       </c>
       <c r="E41">
-        <v>-18.38171206020266</v>
+        <v>-17.58809246188442</v>
       </c>
       <c r="F41">
-        <v>2.332224371862152</v>
+        <v>1.331899493385108</v>
       </c>
       <c r="G41">
-        <v>-2.679718926885857</v>
+        <v>-2.700072160861296</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.697592071045185</v>
       </c>
       <c r="E42">
-        <v>-16.75093611445644</v>
+        <v>-17.76275117588626</v>
       </c>
       <c r="F42">
-        <v>2.01267501929302</v>
+        <v>1.385030978600668</v>
       </c>
       <c r="G42">
-        <v>-1.977204610724815</v>
+        <v>-2.573668911080844</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.382591402632578</v>
       </c>
       <c r="E43">
-        <v>-16.58935110491474</v>
+        <v>-16.23465837826397</v>
       </c>
       <c r="F43">
-        <v>1.89760318990053</v>
+        <v>1.307007052930983</v>
       </c>
       <c r="G43">
-        <v>-2.184772505491579</v>
+        <v>-2.27071095714552</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.066901267745624</v>
       </c>
       <c r="E44">
-        <v>-16.97457027485123</v>
+        <v>-16.72608384910234</v>
       </c>
       <c r="F44">
-        <v>1.880921527142953</v>
+        <v>1.235886741196229</v>
       </c>
       <c r="G44">
-        <v>-2.074941846680718</v>
+        <v>-1.285297282471597</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.769173709166999</v>
       </c>
       <c r="E45">
-        <v>-15.75637906746985</v>
+        <v>-15.3137343186421</v>
       </c>
       <c r="F45">
-        <v>1.822289682372804</v>
+        <v>0.9570151983089695</v>
       </c>
       <c r="G45">
-        <v>-1.698714898870244</v>
+        <v>-1.217702563650758</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.508077761384277</v>
       </c>
       <c r="E46">
-        <v>-15.5501297187905</v>
+        <v>-15.17462865407448</v>
       </c>
       <c r="F46">
-        <v>1.694422890076673</v>
+        <v>0.8517992842749875</v>
       </c>
       <c r="G46">
-        <v>-2.120147346019466</v>
+        <v>-1.318051820037146</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.289205010456043</v>
       </c>
       <c r="E47">
-        <v>-14.69514476919433</v>
+        <v>-15.63805909859744</v>
       </c>
       <c r="F47">
-        <v>1.527662591484299</v>
+        <v>0.8655650937747097</v>
       </c>
       <c r="G47">
-        <v>-1.506428482312756</v>
+        <v>-1.973784817182748</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.125883104173982</v>
       </c>
       <c r="E48">
-        <v>-13.53867666253749</v>
+        <v>-14.47084945159441</v>
       </c>
       <c r="F48">
-        <v>1.500926205191542</v>
+        <v>0.8402352753319063</v>
       </c>
       <c r="G48">
-        <v>-1.505551187744849</v>
+        <v>-1.255217665701779</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.010376580545001</v>
       </c>
       <c r="E49">
-        <v>-13.72282705805941</v>
+        <v>-13.88035002641622</v>
       </c>
       <c r="F49">
-        <v>1.528138074373505</v>
+        <v>0.748576422212141</v>
       </c>
       <c r="G49">
-        <v>-1.307153504121866</v>
+        <v>-1.39507497255383</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.948037838399789</v>
       </c>
       <c r="E50">
-        <v>-13.53264926363328</v>
+        <v>-13.07981997676228</v>
       </c>
       <c r="F50">
-        <v>1.398859744023003</v>
+        <v>0.5641984056970272</v>
       </c>
       <c r="G50">
-        <v>-1.359185348362591</v>
+        <v>-1.478037243767966</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.925744709722709</v>
       </c>
       <c r="E51">
-        <v>-13.86122175220782</v>
+        <v>-12.65017647681055</v>
       </c>
       <c r="F51">
-        <v>1.329308360149151</v>
+        <v>0.7842508927811046</v>
       </c>
       <c r="G51">
-        <v>-0.912923809668835</v>
+        <v>-1.758072980389376</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.940749922584308</v>
       </c>
       <c r="E52">
-        <v>-12.57825072414672</v>
+        <v>-12.83619260362362</v>
       </c>
       <c r="F52">
-        <v>1.218333635930907</v>
+        <v>0.5335123636277223</v>
       </c>
       <c r="G52">
-        <v>-1.771907750197991</v>
+        <v>-2.049083175473471</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.982369315864337</v>
       </c>
       <c r="E53">
-        <v>-12.2404220347005</v>
+        <v>-12.09371306227401</v>
       </c>
       <c r="F53">
-        <v>1.125645950496865</v>
+        <v>0.5538239323443661</v>
       </c>
       <c r="G53">
-        <v>-2.097291339616338</v>
+        <v>-2.312314582937541</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.042699572592964</v>
       </c>
       <c r="E54">
-        <v>-11.8311657247313</v>
+        <v>-11.58287855183875</v>
       </c>
       <c r="F54">
-        <v>0.8643391100185664</v>
+        <v>0.5006849918221806</v>
       </c>
       <c r="G54">
-        <v>-2.594644527617666</v>
+        <v>-2.450562964657506</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.117139556871543</v>
       </c>
       <c r="E55">
-        <v>-11.97300205912554</v>
+        <v>-11.94691352036735</v>
       </c>
       <c r="F55">
-        <v>1.069747718155954</v>
+        <v>0.6346320008548607</v>
       </c>
       <c r="G55">
-        <v>-1.844054469135328</v>
+        <v>-2.257740239722655</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.195631917662873</v>
       </c>
       <c r="E56">
-        <v>-10.89848574658552</v>
+        <v>-10.98432297140091</v>
       </c>
       <c r="F56">
-        <v>0.9654877401048029</v>
+        <v>0.3172281198589797</v>
       </c>
       <c r="G56">
-        <v>-2.751670323636377</v>
+        <v>-2.802377949661394</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.28044330544464</v>
       </c>
       <c r="E57">
-        <v>-11.69670174602154</v>
+        <v>-11.20524457586511</v>
       </c>
       <c r="F57">
-        <v>0.82893303048811</v>
+        <v>0.4546799513729045</v>
       </c>
       <c r="G57">
-        <v>-3.334313096365949</v>
+        <v>-3.251125708055143</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.361673512004685</v>
       </c>
       <c r="E58">
-        <v>-10.50678180187005</v>
+        <v>-10.19321667615693</v>
       </c>
       <c r="F58">
-        <v>1.057656867544693</v>
+        <v>0.3039295095744364</v>
       </c>
       <c r="G58">
-        <v>-2.824280518949212</v>
+        <v>-3.429239679159011</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.445226409295541</v>
       </c>
       <c r="E59">
-        <v>-10.85906990882276</v>
+        <v>-10.12272192127953</v>
       </c>
       <c r="F59">
-        <v>0.8230980105027902</v>
+        <v>0.4066031640492268</v>
       </c>
       <c r="G59">
-        <v>-3.301614838074567</v>
+        <v>-3.851801022337125</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.523554492558866</v>
       </c>
       <c r="E60">
-        <v>-10.14454463752249</v>
+        <v>-9.327091680501884</v>
       </c>
       <c r="F60">
-        <v>0.8207752683053404</v>
+        <v>0.1904696831477938</v>
       </c>
       <c r="G60">
-        <v>-3.08947176937253</v>
+        <v>-3.836261321575785</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.599745076320239</v>
       </c>
       <c r="E61">
-        <v>-10.7449161360374</v>
+        <v>-10.73069672765332</v>
       </c>
       <c r="F61">
-        <v>0.4760079268927834</v>
+        <v>0.5543101840098095</v>
       </c>
       <c r="G61">
-        <v>-4.212660417754302</v>
+        <v>-4.568345430493598</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.668930103062586</v>
       </c>
       <c r="E62">
-        <v>-9.463991978227767</v>
+        <v>-9.024924723866071</v>
       </c>
       <c r="F62">
-        <v>0.7457748836558732</v>
+        <v>0.3767786240788334</v>
       </c>
       <c r="G62">
-        <v>-4.040290243161069</v>
+        <v>-4.313774410160262</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.728588762075344</v>
       </c>
       <c r="E63">
-        <v>-10.15099771298342</v>
+        <v>-9.037414255179227</v>
       </c>
       <c r="F63">
-        <v>0.652553729614428</v>
+        <v>0.0662709017112583</v>
       </c>
       <c r="G63">
-        <v>-4.624512146112873</v>
+        <v>-4.730793900105635</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.777122177247957</v>
       </c>
       <c r="E64">
-        <v>-9.009487155973924</v>
+        <v>-9.44970011425956</v>
       </c>
       <c r="F64">
-        <v>0.6360708750335234</v>
+        <v>0.4097650424257125</v>
       </c>
       <c r="G64">
-        <v>-4.574099158640851</v>
+        <v>-4.900240862987691</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.807641165872207</v>
       </c>
       <c r="E65">
-        <v>-9.501533027751353</v>
+        <v>-8.51315281931123</v>
       </c>
       <c r="F65">
-        <v>0.5529160416708978</v>
+        <v>0.4396815311778167</v>
       </c>
       <c r="G65">
-        <v>-5.375615339153798</v>
+        <v>-4.736987930809612</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.823374321073439</v>
       </c>
       <c r="E66">
-        <v>-9.769605103583416</v>
+        <v>-9.601295310140332</v>
       </c>
       <c r="F66">
-        <v>0.4983158610501741</v>
+        <v>0.09813653896214967</v>
       </c>
       <c r="G66">
-        <v>-5.125586387300342</v>
+        <v>-5.284207866268981</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.816094049104859</v>
       </c>
       <c r="E67">
-        <v>-9.699237145978227</v>
+        <v>-8.74266041049397</v>
       </c>
       <c r="F67">
-        <v>0.3392999693065725</v>
+        <v>0.05795906319156806</v>
       </c>
       <c r="G67">
-        <v>-5.013809127712389</v>
+        <v>-5.070608157529666</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.792997155786824</v>
       </c>
       <c r="E68">
-        <v>-8.814962026500435</v>
+        <v>-8.53414682481079</v>
       </c>
       <c r="F68">
-        <v>0.2421780331653445</v>
+        <v>0.09464662709415536</v>
       </c>
       <c r="G68">
-        <v>-5.17138116374508</v>
+        <v>-5.328678424498012</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.749596094825743</v>
       </c>
       <c r="E69">
-        <v>-9.583801815048702</v>
+        <v>-8.813771037836419</v>
       </c>
       <c r="F69">
-        <v>0.02467443257968112</v>
+        <v>-0.08748651375937194</v>
       </c>
       <c r="G69">
-        <v>-5.105266258780295</v>
+        <v>-5.090203276576611</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.694484027544284</v>
       </c>
       <c r="E70">
-        <v>-9.744970204981689</v>
+        <v>-9.780505140519878</v>
       </c>
       <c r="F70">
-        <v>0.0664398886614294</v>
+        <v>-0.3647195459238937</v>
       </c>
       <c r="G70">
-        <v>-5.412501437552358</v>
+        <v>-5.792330258909559</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.630074870128122</v>
       </c>
       <c r="E71">
-        <v>-9.535442241120791</v>
+        <v>-9.157409759434476</v>
       </c>
       <c r="F71">
-        <v>0.01155060781712855</v>
+        <v>-0.3277876136374805</v>
       </c>
       <c r="G71">
-        <v>-5.046341858726808</v>
+        <v>-5.310566429852659</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.563098980523213</v>
       </c>
       <c r="E72">
-        <v>-9.60192023955339</v>
+        <v>-8.908271233428483</v>
       </c>
       <c r="F72">
-        <v>0.3092053815628665</v>
+        <v>-0.2566441076154478</v>
       </c>
       <c r="G72">
-        <v>-5.984292242004199</v>
+        <v>-4.916532057586445</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.500377835484262</v>
       </c>
       <c r="E73">
-        <v>-9.043930729276264</v>
+        <v>-10.51868263156221</v>
       </c>
       <c r="F73">
-        <v>0.07708275305259744</v>
+        <v>-0.1086363902876489</v>
       </c>
       <c r="G73">
-        <v>-5.320272949373802</v>
+        <v>-4.890398611099438</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.442364959353201</v>
       </c>
       <c r="E74">
-        <v>-9.9982522847047</v>
+        <v>-9.25852152707774</v>
       </c>
       <c r="F74">
-        <v>-0.08793631725909207</v>
+        <v>-0.2632445390809542</v>
       </c>
       <c r="G74">
-        <v>-5.581186974960382</v>
+        <v>-4.757999963347365</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.394974705094219</v>
       </c>
       <c r="E75">
-        <v>-10.52883547028741</v>
+        <v>-9.090682694931454</v>
       </c>
       <c r="F75">
-        <v>0.4009454146881062</v>
+        <v>-0.2992288190585647</v>
       </c>
       <c r="G75">
-        <v>-4.837373603196932</v>
+        <v>-4.9772408416856</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.349128695581297</v>
       </c>
       <c r="E76">
-        <v>-10.57473608282915</v>
+        <v>-9.158655089786585</v>
       </c>
       <c r="F76">
-        <v>-0.3026864245978499</v>
+        <v>-0.4804954876087638</v>
       </c>
       <c r="G76">
-        <v>-4.540046887223908</v>
+        <v>-5.058931863412656</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.306629093726613</v>
       </c>
       <c r="E77">
-        <v>-11.09450980095555</v>
+        <v>-10.28507677140253</v>
       </c>
       <c r="F77">
-        <v>-0.07045030975339731</v>
+        <v>-0.6371695847046511</v>
       </c>
       <c r="G77">
-        <v>-4.391555677605438</v>
+        <v>-4.54921378782215</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.254114249751723</v>
       </c>
       <c r="E78">
-        <v>-11.1402972016471</v>
+        <v>-11.19834318147742</v>
       </c>
       <c r="F78">
-        <v>0.2680413202155507</v>
+        <v>-0.1951113202006949</v>
       </c>
       <c r="G78">
-        <v>-4.216765494222998</v>
+        <v>-4.544175137511379</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.189057769905308</v>
       </c>
       <c r="E79">
-        <v>-11.53887989838022</v>
+        <v>-11.47266907991408</v>
       </c>
       <c r="F79">
-        <v>0.06988838215928374</v>
+        <v>-0.5372096618414319</v>
       </c>
       <c r="G79">
-        <v>-4.379525155115727</v>
+        <v>-4.24101192975262</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.102262235424546</v>
       </c>
       <c r="E80">
-        <v>-11.33375361125478</v>
+        <v>-12.57557892448219</v>
       </c>
       <c r="F80">
-        <v>-0.2662713935707836</v>
+        <v>-0.4024707335716756</v>
       </c>
       <c r="G80">
-        <v>-4.579458931868931</v>
+        <v>-4.083357130081447</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.991592118632612</v>
       </c>
       <c r="E81">
-        <v>-13.80359239198621</v>
+        <v>-11.80159026098721</v>
       </c>
       <c r="F81">
-        <v>0.03823977716792583</v>
+        <v>-0.701354804543168</v>
       </c>
       <c r="G81">
-        <v>-4.112178739546342</v>
+        <v>-3.992032420835113</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.8589880113828</v>
       </c>
       <c r="E82">
-        <v>-13.32397265288583</v>
+        <v>-12.91894140916578</v>
       </c>
       <c r="F82">
-        <v>-0.03667942747606706</v>
+        <v>-0.4062381485196077</v>
       </c>
       <c r="G82">
-        <v>-3.828008131546382</v>
+        <v>-3.672753477391181</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.707512827314766</v>
       </c>
       <c r="E83">
-        <v>-14.42867124468697</v>
+        <v>-14.24419932751051</v>
       </c>
       <c r="F83">
-        <v>-0.5487629020082766</v>
+        <v>-0.5851216040519526</v>
       </c>
       <c r="G83">
-        <v>-4.50760685148459</v>
+        <v>-4.142145797767825</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.550658043022736</v>
       </c>
       <c r="E84">
-        <v>-15.51638353048535</v>
+        <v>-15.04731966429684</v>
       </c>
       <c r="F84">
-        <v>-0.3866166098494958</v>
+        <v>-0.7290620374320058</v>
       </c>
       <c r="G84">
-        <v>-3.464156002961704</v>
+        <v>-3.665586146298659</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.39266050495491</v>
       </c>
       <c r="E85">
-        <v>-16.00543608094371</v>
+        <v>-16.22107748471496</v>
       </c>
       <c r="F85">
-        <v>-0.5209595785007141</v>
+        <v>-0.8946079494118758</v>
       </c>
       <c r="G85">
-        <v>-3.724659520901414</v>
+        <v>-3.795770039084959</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.249912400196696</v>
       </c>
       <c r="E86">
-        <v>-17.6885068445305</v>
+        <v>-17.80208550111688</v>
       </c>
       <c r="F86">
-        <v>-0.4425852534196444</v>
+        <v>-0.9500969682558035</v>
       </c>
       <c r="G86">
-        <v>-3.65136404266195</v>
+        <v>-3.51427766242627</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.124713843042462</v>
       </c>
       <c r="E87">
-        <v>-18.43987125188317</v>
+        <v>-18.35734434156738</v>
       </c>
       <c r="F87">
-        <v>-0.4631262799068637</v>
+        <v>-0.7437456780140299</v>
       </c>
       <c r="G87">
-        <v>-2.658197070335055</v>
+        <v>-4.062325234270458</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.028220984126386</v>
       </c>
       <c r="E88">
-        <v>-19.2943580693385</v>
+        <v>-19.64153352913655</v>
       </c>
       <c r="F88">
-        <v>-0.5232193647755511</v>
+        <v>-0.9124211620416764</v>
       </c>
       <c r="G88">
-        <v>-2.49783093386722</v>
+        <v>-2.934505132679246</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.960786906760145</v>
       </c>
       <c r="E89">
-        <v>-21.85174583806022</v>
+        <v>-21.59481380828703</v>
       </c>
       <c r="F89">
-        <v>-0.6275779185476356</v>
+        <v>-0.9895579062229636</v>
       </c>
       <c r="G89">
-        <v>-3.080698823693462</v>
+        <v>-2.494334997777749</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.924032509441403</v>
       </c>
       <c r="E90">
-        <v>-22.51704659689711</v>
+        <v>-23.01608896101639</v>
       </c>
       <c r="F90">
-        <v>-0.676850040033553</v>
+        <v>-1.360004637122305</v>
       </c>
       <c r="G90">
-        <v>-2.634804755554565</v>
+        <v>-2.849073194492814</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.915484393064817</v>
       </c>
       <c r="E91">
-        <v>-24.48631691776868</v>
+        <v>-23.86671751861719</v>
       </c>
       <c r="F91">
-        <v>-0.7003044346764182</v>
+        <v>-0.9619103157871273</v>
       </c>
       <c r="G91">
-        <v>-3.280486936442939</v>
+        <v>-3.875842204043312</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.927211997038269</v>
       </c>
       <c r="E92">
-        <v>-25.89706336843021</v>
+        <v>-26.41798731895455</v>
       </c>
       <c r="F92">
-        <v>-1.081247408936632</v>
+        <v>-1.201976987690244</v>
       </c>
       <c r="G92">
-        <v>-3.46163336726078</v>
+        <v>-3.17177855256989</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.956677761140661</v>
       </c>
       <c r="E93">
-        <v>-28.03875080866981</v>
+        <v>-28.27234761188148</v>
       </c>
       <c r="F93">
-        <v>-0.7875613434177069</v>
+        <v>-0.8536874280809831</v>
       </c>
       <c r="G93">
-        <v>-3.806933198643382</v>
+        <v>-3.430858535927714</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.99178097462103</v>
       </c>
       <c r="E94">
-        <v>-30.13211490277356</v>
+        <v>-29.27086254515077</v>
       </c>
       <c r="F94">
-        <v>-1.105839152023541</v>
+        <v>-1.359578027909863</v>
       </c>
       <c r="G94">
-        <v>-3.41357086712164</v>
+        <v>-3.651602401940778</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.033360708428136</v>
       </c>
       <c r="E95">
-        <v>-32.45773990025672</v>
+        <v>-32.37588546833108</v>
       </c>
       <c r="F95">
-        <v>-1.058818533138433</v>
+        <v>-1.298100741111098</v>
       </c>
       <c r="G95">
-        <v>-4.140328308266765</v>
+        <v>-4.635029749291138</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.074384928720516</v>
       </c>
       <c r="E96">
-        <v>-33.98773918543624</v>
+        <v>-34.75164973002716</v>
       </c>
       <c r="F96">
-        <v>-1.136832518399285</v>
+        <v>-1.403101279620352</v>
       </c>
       <c r="G96">
-        <v>-4.031480881481068</v>
+        <v>-4.252069151853786</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.11734772689443</v>
       </c>
       <c r="E97">
-        <v>-36.72360996445928</v>
+        <v>-36.53153700366094</v>
       </c>
       <c r="F97">
-        <v>-1.344505883015926</v>
+        <v>-1.848791106818181</v>
       </c>
       <c r="G97">
-        <v>-4.658392269161774</v>
+        <v>-4.169583599197305</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.167106517644223</v>
       </c>
       <c r="E98">
-        <v>-39.21837346612892</v>
+        <v>-39.31577867779691</v>
       </c>
       <c r="F98">
-        <v>-1.624547080675939</v>
+        <v>-1.338921029986252</v>
       </c>
       <c r="G98">
-        <v>-4.59245944420165</v>
+        <v>-4.607320483127437</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.2226991838798</v>
       </c>
       <c r="E99">
-        <v>-42.10459637491763</v>
+        <v>-42.32004758278056</v>
       </c>
       <c r="F99">
-        <v>-1.524505977807245</v>
+        <v>-1.515190157995362</v>
       </c>
       <c r="G99">
-        <v>-5.301197585976522</v>
+        <v>-4.478229070369097</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.3019492195159</v>
       </c>
       <c r="E100">
-        <v>-43.74603914118891</v>
+        <v>-43.98351684662515</v>
       </c>
       <c r="F100">
-        <v>-1.719357043395953</v>
+        <v>-1.468595319955292</v>
       </c>
       <c r="G100">
-        <v>-5.390840538088907</v>
+        <v>-4.614272628759907</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.389072891864869</v>
       </c>
       <c r="E101">
-        <v>-45.81520307019567</v>
+        <v>-46.45159857944161</v>
       </c>
       <c r="F101">
-        <v>-2.173129251342897</v>
+        <v>-1.964248955420377</v>
       </c>
       <c r="G101">
-        <v>-5.2758553598734</v>
+        <v>-5.613411825239647</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.52247929315689</v>
       </c>
       <c r="E102">
-        <v>-48.1537976172368</v>
+        <v>-49.10866711802016</v>
       </c>
       <c r="F102">
-        <v>-2.336861867078039</v>
+        <v>-2.199096084318453</v>
       </c>
       <c r="G102">
-        <v>-5.588950204249973</v>
+        <v>-5.65037406618561</v>
       </c>
     </row>
   </sheetData>
